--- a/Result/profitability/3527.xlsx
+++ b/Result/profitability/3527.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>2.2</v>
       </c>
       <c r="M2" t="n">
-        <v>0.006250000000000033</v>
+        <v>0.07375000000000004</v>
       </c>
       <c r="N2" t="n">
-        <v>39.05</v>
+        <v>39.48875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>2.17</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3275</v>
+        <v>0.33625</v>
       </c>
       <c r="N3" t="n">
-        <v>39.485</v>
+        <v>39.76875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>3.05</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="N4" t="n">
-        <v>40.17625</v>
+        <v>40.16625000000001</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.47</v>
       </c>
       <c r="M5" t="n">
-        <v>0.87625</v>
+        <v>1.01375</v>
       </c>
       <c r="N5" t="n">
-        <v>40.6225</v>
+        <v>40.915</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.25</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1525</v>
+        <v>1.18875</v>
       </c>
       <c r="N6" t="n">
-        <v>41.6575</v>
+        <v>42.035</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1.04</v>
       </c>
       <c r="M7" t="n">
-        <v>1.30125</v>
+        <v>1.41625</v>
       </c>
       <c r="N7" t="n">
-        <v>42.1425</v>
+        <v>42.2025</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
         <v>98.2</v>
@@ -1391,10 +1391,10 @@
         <v>1.76</v>
       </c>
       <c r="M8" t="n">
-        <v>1.61875</v>
+        <v>1.635</v>
       </c>
       <c r="N8" t="n">
-        <v>41.97750000000001</v>
+        <v>42.06125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>1.985</v>
       </c>
       <c r="N11" t="n">
-        <v>42.7125</v>
+        <v>42.71250000000001</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3527</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>389</v>
+      </c>
+      <c r="D75" t="n">
+        <v>232</v>
+      </c>
+      <c r="E75" t="n">
+        <v>156</v>
+      </c>
+      <c r="F75" t="n">
+        <v>40.26</v>
+      </c>
+      <c r="G75" t="n">
+        <v>5</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.36%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>9</v>
+      </c>
+      <c r="J75" t="n">
+        <v>14</v>
+      </c>
+      <c r="K75" t="n">
+        <v>6</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.25125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>38.73375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="X75" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.6699999999999946</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.01692346552159618</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.145833333333333</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.339999999999996</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.06170886075949356</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
